--- a/docs/cadrage/equipe-24-sprint-backlog-v1.0.xlsx
+++ b/docs/cadrage/equipe-24-sprint-backlog-v1.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabriel/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D700C880-0285-4E5D-96B6-9CA89D048CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{D700C880-0285-4E5D-96B6-9CA89D048CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29D605EA-451D-4C7C-9870-7FB2E9EE9260}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17780" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17780" tabRatio="500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Garde" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="149">
   <si>
     <t>A</t>
   </si>
@@ -459,10 +459,13 @@
     <t>Métadonnées sprint complètes (numéro, date, équipe, capacité, vélocité cible, objectif, SM/PO)</t>
   </si>
   <si>
-    <t>☐ Oui   ☐ Partiel   ☐ Non</t>
+    <t>☑ Oui   ☐ Partiel   ☐ Non</t>
   </si>
   <si>
     <t>Stories engagées tirées du Product Backlog avec leur ID (US-XX)</t>
+  </si>
+  <si>
+    <t>☑Oui   ☐ Partiel   ☐ Non</t>
   </si>
   <si>
     <t>Chaque story est décomposée en 3-5 tâches techniques atomiques (1-3 h chacune)</t>
@@ -1925,13 +1928,13 @@
         <v>139</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D7" s="32"/>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
       <c r="B8" s="32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C8" s="33" t="s">
         <v>138</v>
@@ -1940,7 +1943,7 @@
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1">
       <c r="B9" s="32" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>138</v>
@@ -1949,7 +1952,7 @@
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1">
       <c r="B10" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>138</v>
@@ -1958,7 +1961,7 @@
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1">
       <c r="B11" s="32" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>138</v>
@@ -1967,7 +1970,7 @@
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1">
       <c r="B12" s="32" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C12" s="33" t="s">
         <v>138</v>
@@ -1976,16 +1979,16 @@
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1">
       <c r="B13" s="32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D13" s="32"/>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
       <c r="B14" s="32" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C14" s="33" t="s">
         <v>138</v>
@@ -1994,10 +1997,10 @@
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1">
       <c r="B15" s="32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D15" s="32"/>
     </row>
@@ -2008,6 +2011,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010047E35FF551331140B273BB19EEA78143" ma:contentTypeVersion="3" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="530aa9c009d146a80c49f02630cdfc2d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aa7a771e-02cb-4c1a-a357-20624cfae5a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d97f7f33240c9425ea547835b506498e" ns2:_="">
     <xsd:import namespace="aa7a771e-02cb-4c1a-a357-20624cfae5a5"/>
@@ -2145,23 +2163,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CC135BE-3FF2-48B8-8233-3C0C44AFC8C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEEB1A03-4C8B-4DE7-AFE5-2A39ADA08CF2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2169,5 +2172,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEEB1A03-4C8B-4DE7-AFE5-2A39ADA08CF2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CC135BE-3FF2-48B8-8233-3C0C44AFC8C3}"/>
 </file>